--- a/bot-ventas/resultados/consolidado_limpio.xlsx
+++ b/bot-ventas/resultados/consolidado_limpio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,41 +452,6 @@
           <t>metodo_pago</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Fecha_Venta</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cant</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Valor_Unitario</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Vendedor</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -520,13 +485,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,13 +518,6 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,13 +551,6 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,13 +584,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,13 +617,6 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -720,13 +650,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -756,13 +679,6 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -796,13 +712,6 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -836,13 +745,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -876,13 +778,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -912,13 +807,6 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -952,13 +840,6 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,13 +873,6 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1028,39 +902,32 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>55400</v>
+        <v>142300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1068,39 +935,32 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>20200</v>
+        <v>103400</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1108,59 +968,49 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>107600</v>
+        <v>167200</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Sofia Mena</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1169,38 +1019,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>148600</v>
+        <v>56100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1209,38 +1052,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>40700</v>
+        <v>98700</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1252,35 +1088,28 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>74200</v>
+        <v>145600</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1289,38 +1118,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>175600</v>
+        <v>73800</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1329,38 +1151,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>110300</v>
+        <v>112500</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1369,86 +1184,76 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>156100</v>
+        <v>28900</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>41800</v>
+        <v>74300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>115500</v>
+        <v>55400</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1457,26 +1262,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1488,11 +1286,11 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>59500</v>
+        <v>20200</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1500,23 +1298,16 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1525,130 +1316,109 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>150600</v>
+        <v>107600</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>165700</v>
+        <v>148600</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>80300</v>
+        <v>40700</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>137900</v>
+        <v>74200</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1656,95 +1426,82 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>74700</v>
+        <v>175600</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>40200</v>
+        <v>110300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1753,128 +1510,105 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>90600</v>
+        <v>156100</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>98500</v>
+        <v>41800</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>115500</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>125200</v>
+        <v>59500</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1883,26 +1617,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1911,29 +1638,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+        <v>150600</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1950,11 +1670,11 @@
         <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>133400</v>
+        <v>165700</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1962,63 +1682,49 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>164400</v>
+        <v>80300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2027,12 +1733,14 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>137900</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2040,99 +1748,74 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>107500</v>
+        <v>74700</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>152700</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+        <v>40200</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2141,33 +1824,26 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>65900</v>
+        <v>185000</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2183,82 +1859,78 @@
       <c r="D45" t="n">
         <v>4</v>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>92300</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>157700</v>
+        <v>134500</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>144100</v>
+        <v>48700</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2266,23 +1938,16 @@
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2291,652 +1956,1171 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>78100</v>
+        <v>156800</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chaqueta impermeable</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>178900</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cargador USB-C</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>72400</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mouse inalambrico</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>89200</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Medias deportivas</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>31500</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gorra deportiva</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>67800</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chaqueta impermeable</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>90600</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Camiseta basica</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>98500</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Camiseta basica</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Medias deportivas</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>125200</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Camiseta basica</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cargador USB-C</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>133400</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Parlante portatil</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>164400</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Teclado mecanico</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mouse inalambrico</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" t="n">
+        <v>107500</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mouse inalambrico</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>152700</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Teclado mecanico</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>65900</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Jean clasico</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Medias deportivas</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>157700</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Audifonos Bluetooth</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="n">
+        <v>144100</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cargador USB-C</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>78100</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Jean clasico</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>8</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E69" t="n">
         <v>72700</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Medias deportivas</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>7</v>
       </c>
-      <c r="L50" t="n">
+      <c r="E70" t="n">
         <v>78000</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Felipe Torres</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Parlante portatil</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Electronica</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>2</v>
       </c>
-      <c r="L51" t="n">
+      <c r="E71" t="n">
         <v>127500</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Sofia Mena</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Chaqueta impermeable</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="L52" t="n">
+      <c r="E72" t="n">
         <v>86700</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Felipe Torres</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Cargador USB-C</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Electronica</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>3</v>
       </c>
-      <c r="L53" t="n">
+      <c r="E73" t="n">
         <v>98800</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Parlante portatil</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Electronica</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>4</v>
       </c>
-      <c r="L54" t="n">
+      <c r="E74" t="n">
         <v>40200</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Medias deportivas</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>8</v>
       </c>
-      <c r="L55" t="n">
+      <c r="E75" t="n">
         <v>18200</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Laura Diaz</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Jean clasico</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>4</v>
       </c>
-      <c r="L56" t="n">
+      <c r="E76" t="n">
         <v>159900</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Gorra deportiva</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>3</v>
       </c>
-      <c r="L57" t="n">
+      <c r="E77" t="n">
         <v>36200</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Felipe Torres</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Cargador USB-C</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Electronica</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
         <v>7</v>
       </c>
-      <c r="L58" t="n">
+      <c r="E78" t="n">
         <v>174100</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Sofia Mena</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Cargador USB-C</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Electronica</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Electronica</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
         <v>6</v>
       </c>
-      <c r="L59" t="n">
+      <c r="E79" t="n">
         <v>87300</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Sofia Mena</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Camiseta basica</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
         <v>4</v>
       </c>
-      <c r="L60" t="n">
+      <c r="E80" t="n">
         <v>25600</v>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Medias deportivas</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="L61" t="n">
+      <c r="E81" t="n">
         <v>26700</v>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Tarjeta</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Camiseta basica</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
         <v>6</v>
       </c>
-      <c r="L62" t="n">
+      <c r="E82" t="n">
         <v>26700</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Gorra deportiva</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
         <v>3</v>
       </c>
-      <c r="L63" t="n">
+      <c r="E83" t="n">
         <v>134400</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Sofia Mena</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Jean clasico</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
         <v>7</v>
       </c>
-      <c r="L64" t="n">
+      <c r="E84" t="n">
         <v>46400</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bot-ventas/resultados/consolidado_limpio.xlsx
+++ b/bot-ventas/resultados/consolidado_limpio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,12 +906,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Teclado</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -923,11 +923,11 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>142300</v>
+        <v>65000</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Falda</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -953,14 +953,14 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>103400</v>
+        <v>52000</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -972,12 +972,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Audifonos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,31 +986,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>167200</v>
+        <v>38000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Chaqueta</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>56100</v>
+        <v>120000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1052,31 +1052,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>98700</v>
+        <v>142300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>145600</v>
+        <v>103400</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,97 +1118,97 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>73800</v>
+        <v>167200</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>112500</v>
+        <v>56100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>28900</v>
+        <v>98700</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1217,14 +1217,14 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>74300</v>
+        <v>145600</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1236,24 +1236,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>55400</v>
+        <v>73800</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1262,19 +1262,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1283,31 +1283,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>20200</v>
+        <v>112500</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1316,27 +1316,31 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>107600</v>
+        <v>28900</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1345,47 +1349,47 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>148600</v>
+        <v>74300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>40700</v>
+        <v>55400</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1397,90 +1401,86 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>74200</v>
+        <v>20200</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>175600</v>
+        <v>107600</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>110300</v>
+        <v>148600</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1489,60 +1489,64 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>156100</v>
+        <v>40700</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>41800</v>
+        <v>74200</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1551,19 +1555,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1575,28 +1579,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>115500</v>
+        <v>175600</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1605,31 +1609,31 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>59500</v>
+        <v>110300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1638,14 +1642,14 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>150600</v>
+        <v>156100</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1653,7 +1657,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1667,47 +1671,47 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>165700</v>
+        <v>41800</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>80300</v>
+        <v>115500</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1719,12 +1723,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1733,10 +1737,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>137900</v>
+        <v>59500</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1745,19 +1749,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1766,14 +1770,14 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>74700</v>
+        <v>150600</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1781,57 +1785,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>40200</v>
+        <v>165700</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>185000</v>
+        <v>80300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1843,73 +1851,69 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>92300</v>
+        <v>137900</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>134500</v>
+        <v>74700</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1923,31 +1927,27 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>48700</v>
+        <v>40200</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1956,31 +1956,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>156800</v>
+        <v>185000</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1989,31 +1989,31 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>178900</v>
+        <v>92300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2022,80 +2022,80 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>72400</v>
+        <v>134500</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>89200</v>
+        <v>48700</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>31500</v>
+        <v>156800</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2121,14 +2121,14 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>67800</v>
+        <v>178900</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2140,28 +2140,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>90600</v>
+        <v>72400</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2173,28 +2173,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>98500</v>
+        <v>89200</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2206,12 +2206,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2220,29 +2220,31 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>31500</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2251,31 +2253,31 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>125200</v>
+        <v>67800</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2284,39 +2286,43 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
+        <v>90600</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>133400</v>
+        <v>98500</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2332,59 +2338,59 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>164400</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>125200</v>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2396,45 +2402,41 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>107500</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
+        <v>34000</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2443,27 +2445,31 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>152700</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
+        <v>133400</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2472,10 +2478,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>65900</v>
+        <v>164400</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2484,75 +2490,83 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>157700</v>
+        <v>107500</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2561,16 +2575,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>144100</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Felipe Torres</t>
-        </is>
-      </c>
+        <v>152700</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>Tarjeta</t>
@@ -2580,12 +2590,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2594,22 +2604,26 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>78100</v>
+        <v>65900</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2623,26 +2637,20 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
-      </c>
-      <c r="E69" t="n">
-        <v>72700</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2656,31 +2664,27 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>78000</v>
+        <v>157700</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2689,146 +2693,142 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>127500</v>
+        <v>144100</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>86700</v>
+        <v>78100</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>98800</v>
+        <v>72700</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>40200</v>
+        <v>78000</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>18200</v>
+        <v>127500</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2840,12 +2840,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2854,14 +2854,14 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>159900</v>
+        <v>86700</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2873,45 +2873,45 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>36200</v>
+        <v>98800</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2920,60 +2920,64 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>174100</v>
+        <v>40200</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>87300</v>
+        <v>18200</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2985,7 +2989,7 @@
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>25600</v>
+        <v>159900</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2994,19 +2998,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3015,14 +3019,14 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>26700</v>
+        <v>36200</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3034,57 +3038,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>26700</v>
+        <v>174100</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>134400</v>
+        <v>87300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3096,31 +3100,159 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Camiseta basica</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" t="n">
+        <v>25600</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Medias deportivas</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>26700</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Camiseta basica</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>26700</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gorra deportiva</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>134400</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Jean clasico</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
         <v>7</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E88" t="n">
         <v>46400</v>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Camila Ruiz</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
